--- a/artfynd/A 26935-2026 artfynd.xlsx
+++ b/artfynd/A 26935-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128423551</v>
+        <v>128420365</v>
       </c>
       <c r="B2" t="n">
-        <v>58554</v>
+        <v>91039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>1334</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gyllensopp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Aureoboletus gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+          <t>(Quél.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nyborg 2, Ög</t>
@@ -759,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,69 +767,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128420365</v>
+        <v>128410482</v>
       </c>
       <c r="B3" t="n">
-        <v>90654</v>
+        <v>87375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1334</v>
+        <v>3739</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyllensopp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aureoboletus gentilis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Pouzar</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nyborg 2, Ög</t>
+          <t>Nyborg, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570011</v>
+        <v>570045</v>
       </c>
       <c r="R3" t="n">
-        <v>6479065</v>
+        <v>6479063</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,7 +846,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Västra Husby</t>
+          <t>Drothem</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +866,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Med tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,22 +880,142 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128423551</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nyborg 2, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570011</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6479065</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Husby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26935-2026 artfynd.xlsx
+++ b/artfynd/A 26935-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,6 +1017,122 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134573390</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570051</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6479123</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Suvi Bergström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26935-2026 artfynd.xlsx
+++ b/artfynd/A 26935-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128420365</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410482</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423551</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,8 +1152,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134573390</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>